--- a/outputs/monitor_xlsx/20260130.xlsx
+++ b/outputs/monitor_xlsx/20260130.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -1207,13 +1207,13 @@
           <t>個股籌碼監控報告 - 20260130</t>
         </is>
       </c>
-      <c r="P1" s="15" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="15" t="n"/>
+      <c r="R1" s="16" t="n"/>
       <c r="S1" s="16" t="n"/>
       <c r="T1" s="16" t="n"/>
-      <c r="U1" s="16" t="n"/>
-      <c r="V1" s="14" t="n"/>
+      <c r="U1" s="14" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="14" t="n"/>
@@ -1230,14 +1230,13 @@
       <c r="L2" s="15" t="n"/>
       <c r="M2" s="15" t="n"/>
       <c r="N2" s="16" t="n"/>
-      <c r="O2" s="14" t="n"/>
-      <c r="P2" s="15" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="15" t="n"/>
+      <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="16" t="n"/>
-      <c r="U2" s="16" t="n"/>
-      <c r="V2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -1310,42 +1309,37 @@
           <t>MA20乖離(%)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>籌碼評價</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>買賣券商差</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>籌碼集中度5D(%)</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>借券賣出餘額</t>
         </is>
       </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>短回補天數</t>
+        </is>
+      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
           <t>VWAP乖離(%)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1398,30 +1392,25 @@
       <c r="N4" s="8" t="n">
         <v>-0.68</v>
       </c>
-      <c r="O4" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="n">
+      <c r="O4" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="Q4" s="12" t="n">
+      <c r="P4" s="12" t="n">
         <v>-7.15</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="Q4" s="10" t="n">
         <v>116023000</v>
       </c>
+      <c r="R4" s="8" t="n">
+        <v>1.31</v>
+      </c>
       <c r="S4" s="8" t="n">
-        <v>1.31</v>
+        <v>71.37</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>71.37</v>
-      </c>
-      <c r="U4" s="8" t="n">
         <v>1.72</v>
       </c>
-      <c r="V4" s="14" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1464,30 +1453,25 @@
         <v>-23939</v>
       </c>
       <c r="N5" s="16" t="n"/>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="n">
+      <c r="O5" s="10" t="n">
         <v>-24</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="P5" s="9" t="n">
         <v>9.77</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="Q5" s="10" t="n">
         <v>1551000</v>
       </c>
+      <c r="R5" s="8" t="n">
+        <v>1.97</v>
+      </c>
       <c r="S5" s="8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T5" s="8" t="n">
         <v>116.69</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="T5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="14" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1540,30 +1524,25 @@
       <c r="N6" s="8" t="n">
         <v>-5.27</v>
       </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="n">
+      <c r="O6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="P6" s="12" t="n">
         <v>-0.5</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="Q6" s="10" t="n">
         <v>3661000</v>
       </c>
+      <c r="R6" s="8" t="n">
+        <v>0.92</v>
+      </c>
       <c r="S6" s="8" t="n">
-        <v>0.92</v>
+        <v>924.52</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>924.52</v>
-      </c>
-      <c r="U6" s="8" t="n">
         <v>4.92</v>
       </c>
-      <c r="V6" s="14" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1616,30 +1595,25 @@
       <c r="N7" s="8" t="n">
         <v>5.25</v>
       </c>
-      <c r="O7" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="n">
+      <c r="O7" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="P7" s="9" t="n">
         <v>2.74</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="Q7" s="10" t="n">
         <v>172248918</v>
       </c>
+      <c r="R7" s="8" t="n">
+        <v>1.05</v>
+      </c>
       <c r="S7" s="8" t="n">
-        <v>1.05</v>
+        <v>40.88</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>40.88</v>
-      </c>
-      <c r="U7" s="8" t="n">
         <v>6.41</v>
       </c>
-      <c r="V7" s="14" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1692,30 +1666,25 @@
       <c r="N8" s="8" t="n">
         <v>-2.79</v>
       </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="n">
+      <c r="O8" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="P8" s="9" t="n">
         <v>8.27</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="Q8" s="10" t="n">
         <v>2170680</v>
       </c>
+      <c r="R8" s="8" t="n">
+        <v>0.17</v>
+      </c>
       <c r="S8" s="8" t="n">
-        <v>0.17</v>
+        <v>1130.93</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>1130.93</v>
-      </c>
-      <c r="U8" s="8" t="n">
         <v>7.88</v>
       </c>
-      <c r="V8" s="14" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1768,30 +1737,25 @@
       <c r="N9" s="8" t="n">
         <v>-0.62</v>
       </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="n">
+      <c r="O9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="P9" s="12" t="n">
         <v>-7.1</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="Q9" s="10" t="n">
         <v>1550680</v>
       </c>
+      <c r="R9" s="8" t="n">
+        <v>0.05</v>
+      </c>
       <c r="S9" s="8" t="n">
-        <v>0.05</v>
+        <v>1726.08</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>1726.08</v>
-      </c>
-      <c r="U9" s="8" t="n">
         <v>2.83</v>
       </c>
-      <c r="V9" s="14" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1844,30 +1808,25 @@
       <c r="N10" s="8" t="n">
         <v>9.18</v>
       </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="n">
+      <c r="O10" s="10" t="n">
         <v>-16</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="P10" s="12" t="n">
         <v>-4.83</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="Q10" s="10" t="n">
         <v>28385000</v>
       </c>
+      <c r="R10" s="8" t="n">
+        <v>0.15</v>
+      </c>
       <c r="S10" s="8" t="n">
-        <v>0.15</v>
+        <v>110.87</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>110.87</v>
-      </c>
-      <c r="U10" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="V10" s="14" t="inlineStr">
+      <c r="U10" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1920,30 +1879,25 @@
       <c r="N11" s="8" t="n">
         <v>-3.59</v>
       </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="n">
+      <c r="O11" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="P11" s="9" t="n">
         <v>3.91</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="Q11" s="10" t="n">
         <v>2252528</v>
       </c>
+      <c r="R11" s="8" t="n">
+        <v>0.52</v>
+      </c>
       <c r="S11" s="8" t="n">
-        <v>0.52</v>
+        <v>1666.9</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1666.9</v>
-      </c>
-      <c r="U11" s="8" t="n">
         <v>4.69</v>
       </c>
-      <c r="V11" s="14" t="inlineStr">
+      <c r="U11" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1996,30 +1950,25 @@
       <c r="N12" s="8" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="n">
+      <c r="O12" s="10" t="n">
         <v>-21</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="P12" s="9" t="n">
         <v>4.19</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="Q12" s="10" t="n">
         <v>5046503</v>
       </c>
+      <c r="R12" s="8" t="n">
+        <v>2.12</v>
+      </c>
       <c r="S12" s="8" t="n">
-        <v>2.12</v>
+        <v>3473.09</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>3473.09</v>
-      </c>
-      <c r="U12" s="8" t="n">
         <v>-10.02</v>
       </c>
-      <c r="V12" s="14" t="inlineStr">
+      <c r="U12" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2072,30 +2021,25 @@
       <c r="N13" s="8" t="n">
         <v>14.39</v>
       </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="Q13" s="12" t="n">
+      <c r="P13" s="12" t="n">
         <v>-2.47</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="Q13" s="10" t="n">
         <v>19168945</v>
       </c>
+      <c r="R13" s="8" t="n">
+        <v>0.85</v>
+      </c>
       <c r="S13" s="8" t="n">
-        <v>0.85</v>
+        <v>169.85</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>169.85</v>
-      </c>
-      <c r="U13" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="V13" s="14" t="inlineStr">
+      <c r="U13" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2148,30 +2092,25 @@
       <c r="N14" s="8" t="n">
         <v>20.93</v>
       </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P14" s="10" t="n">
+      <c r="O14" s="10" t="n">
         <v>-48</v>
       </c>
-      <c r="Q14" s="12" t="n">
+      <c r="P14" s="12" t="n">
         <v>-3.17</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>2278000</v>
       </c>
+      <c r="R14" s="8" t="n">
+        <v>0.63</v>
+      </c>
       <c r="S14" s="8" t="n">
-        <v>0.63</v>
+        <v>1413.7</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1413.7</v>
-      </c>
-      <c r="U14" s="8" t="n">
         <v>26.26</v>
       </c>
-      <c r="V14" s="14" t="inlineStr">
+      <c r="U14" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2224,30 +2163,25 @@
       <c r="N15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="P15" s="9" t="n">
         <v>1.66</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="Q15" s="10" t="n">
         <v>2469400</v>
       </c>
+      <c r="R15" s="8" t="n">
+        <v>3.53</v>
+      </c>
       <c r="S15" s="8" t="n">
-        <v>3.53</v>
+        <v>764.27</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>764.27</v>
-      </c>
-      <c r="U15" s="8" t="n">
         <v>48.51</v>
       </c>
-      <c r="V15" s="14" t="inlineStr">
+      <c r="U15" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2300,30 +2234,25 @@
       <c r="N16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P16" s="10" t="n">
+      <c r="O16" s="10" t="n">
         <v>-14</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="P16" s="9" t="n">
         <v>9.41</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="Q16" s="10" t="n">
         <v>7587640</v>
       </c>
+      <c r="R16" s="8" t="n">
+        <v>0.39</v>
+      </c>
       <c r="S16" s="8" t="n">
-        <v>0.39</v>
+        <v>333.49</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>333.49</v>
-      </c>
-      <c r="U16" s="8" t="n">
         <v>-0.15</v>
       </c>
-      <c r="V16" s="14" t="inlineStr">
+      <c r="U16" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2376,30 +2305,25 @@
       <c r="N17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="n">
+      <c r="O17" s="10" t="n">
         <v>-44</v>
       </c>
-      <c r="Q17" s="12" t="n">
+      <c r="P17" s="12" t="n">
         <v>-2.45</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>2341000</v>
       </c>
+      <c r="R17" s="8" t="n">
+        <v>2.41</v>
+      </c>
       <c r="S17" s="8" t="n">
-        <v>2.41</v>
+        <v>138.88</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>138.88</v>
-      </c>
-      <c r="U17" s="8" t="n">
         <v>0.45</v>
       </c>
-      <c r="V17" s="14" t="inlineStr">
+      <c r="U17" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2452,30 +2376,25 @@
       <c r="N18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="n">
+      <c r="O18" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="Q18" s="12" t="n">
+      <c r="P18" s="12" t="n">
         <v>-5.35</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="Q18" s="10" t="n">
         <v>11563993</v>
       </c>
+      <c r="R18" s="8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="S18" s="8" t="n">
-        <v>0.5600000000000001</v>
+        <v>302.1</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>302.1</v>
-      </c>
-      <c r="U18" s="8" t="n">
         <v>8.57</v>
       </c>
-      <c r="V18" s="14" t="inlineStr">
+      <c r="U18" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2528,30 +2447,25 @@
       <c r="N19" s="8" t="n">
         <v>12.15</v>
       </c>
-      <c r="O19" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="n">
+      <c r="O19" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="P19" s="9" t="n">
         <v>1.43</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="Q19" s="10" t="n">
         <v>7265826</v>
       </c>
+      <c r="R19" s="8" t="n">
+        <v>0.19</v>
+      </c>
       <c r="S19" s="8" t="n">
-        <v>0.19</v>
+        <v>201.62</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>201.62</v>
-      </c>
-      <c r="U19" s="8" t="n">
         <v>24.99</v>
       </c>
-      <c r="V19" s="14" t="inlineStr">
+      <c r="U19" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2604,11 +2518,6 @@
       <c r="N20" t="n">
         <v>-9.380000000000001</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2657,11 +2566,6 @@
       <c r="N21" t="n">
         <v>3.26</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2710,11 +2614,6 @@
       <c r="N22" t="n">
         <v>-11.19</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2763,11 +2662,6 @@
       <c r="N23" t="n">
         <v>-5.27</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2816,11 +2710,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2868,11 +2757,6 @@
       </c>
       <c r="N25" t="n">
         <v>7.2</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260130.xlsx
+++ b/outputs/monitor_xlsx/20260130.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -199,6 +199,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1174,7 +1186,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -1207,7 +1219,6 @@
           <t>個股籌碼監控報告 - 20260130</t>
         </is>
       </c>
-      <c r="O1" s="15" t="n"/>
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="15" t="n"/>
       <c r="R1" s="16" t="n"/>
@@ -1353,47 +1364,49 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="E4" s="25" t="n">
         <v>-1.56</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="F4" s="24" t="n">
         <v>175275</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="G4" s="24" t="n">
         <v>-63741</v>
       </c>
-      <c r="G4" s="10" t="n">
-        <v>-19014</v>
-      </c>
       <c r="H4" s="10" t="n">
+        <v>-82964</v>
+      </c>
+      <c r="I4" s="10" t="n">
         <v>1640</v>
       </c>
-      <c r="I4" s="10" t="n">
-        <v>2266</v>
-      </c>
       <c r="J4" s="10" t="n">
+        <v>3906</v>
+      </c>
+      <c r="K4" s="10" t="n">
         <v>40555</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="L4" s="10" t="n">
         <v>7371</v>
       </c>
-      <c r="L4" s="10" t="n">
-        <v>35417</v>
-      </c>
       <c r="M4" s="10" t="n">
+        <v>35413</v>
+      </c>
+      <c r="N4" s="8" t="n">
         <v>-3984521</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>-0.68</v>
-      </c>
       <c r="O4" s="10" t="n">
-        <v>-23</v>
+        <v>1.05</v>
       </c>
       <c r="P4" s="12" t="n">
         <v>-7.15</v>
@@ -1488,44 +1501,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
         <v>970</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="E6" s="25" t="n">
         <v>-4.43</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="F6" s="25" t="n">
         <v>3758</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="25" t="n">
         <v>111</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <v>1257</v>
-      </c>
       <c r="H6" s="10" t="n">
+        <v>1537</v>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>-38</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>-538</v>
-      </c>
       <c r="J6" s="10" t="n">
+        <v>-392</v>
+      </c>
+      <c r="K6" s="10" t="n">
         <v>175</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>2626</v>
       </c>
-      <c r="L6" s="10" t="n">
-        <v>14121</v>
-      </c>
       <c r="M6" s="10" t="n">
+        <v>13854</v>
+      </c>
+      <c r="N6" s="8" t="n">
         <v>-78686</v>
       </c>
-      <c r="N6" s="8" t="n">
-        <v>-5.27</v>
-      </c>
       <c r="O6" s="10" t="n">
-        <v>16</v>
+        <v>2.56</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>-0.5</v>
@@ -1630,44 +1645,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
         <v>1220</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="E8" s="25" t="n">
         <v>-2.79</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>10993</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="G8" s="24" t="n">
         <v>-349</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>-3777</v>
-      </c>
       <c r="H8" s="10" t="n">
+        <v>-2703</v>
+      </c>
+      <c r="I8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>1095</v>
-      </c>
       <c r="J8" s="10" t="n">
+        <v>895</v>
+      </c>
+      <c r="K8" s="10" t="n">
         <v>749</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="L8" s="10" t="n">
         <v>6391</v>
       </c>
-      <c r="L8" s="10" t="n">
-        <v>39412</v>
-      </c>
       <c r="M8" s="10" t="n">
+        <v>36956</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>-648604</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>-2.79</v>
-      </c>
       <c r="O8" s="10" t="n">
-        <v>30</v>
+        <v>6.55</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>8.27</v>
@@ -1701,44 +1718,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="n">
         <v>1775</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="E9" s="25" t="n">
         <v>-1.66</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="F9" s="24" t="n">
         <v>46341</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="G9" s="24" t="n">
         <v>-13718</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <v>-3136</v>
-      </c>
       <c r="H9" s="10" t="n">
+        <v>-11936</v>
+      </c>
+      <c r="I9" s="10" t="n">
         <v>450</v>
       </c>
-      <c r="I9" s="10" t="n">
-        <v>3359</v>
-      </c>
       <c r="J9" s="10" t="n">
+        <v>446</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>537</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="L9" s="10" t="n">
         <v>20784</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>100520</v>
-      </c>
       <c r="M9" s="10" t="n">
+        <v>100623</v>
+      </c>
+      <c r="N9" s="8" t="n">
         <v>-6482876</v>
       </c>
-      <c r="N9" s="8" t="n">
-        <v>-0.62</v>
-      </c>
       <c r="O9" s="10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>-7.1</v>
@@ -1843,44 +1862,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="n">
         <v>1745</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="E11" s="25" t="n">
         <v>-2.51</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="F11" s="24" t="n">
         <v>3216</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="G11" s="24" t="n">
         <v>-276</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>2880</v>
-      </c>
       <c r="H11" s="10" t="n">
+        <v>1151</v>
+      </c>
+      <c r="I11" s="10" t="n">
         <v>-36</v>
       </c>
-      <c r="I11" s="10" t="n">
-        <v>-704</v>
-      </c>
       <c r="J11" s="10" t="n">
+        <v>-749</v>
+      </c>
+      <c r="K11" s="10" t="n">
         <v>111</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="L11" s="10" t="n">
         <v>2026</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <v>10340</v>
-      </c>
       <c r="M11" s="10" t="n">
+        <v>10112</v>
+      </c>
+      <c r="N11" s="8" t="n">
         <v>-89494</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>-3.59</v>
-      </c>
       <c r="O11" s="10" t="n">
-        <v>45</v>
+        <v>4.34</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>3.91</v>
@@ -2056,44 +2077,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="n">
         <v>1785</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="24" t="n">
         <v>3.48</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="F14" s="25" t="n">
         <v>8150</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="25" t="n">
         <v>847</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>2360</v>
-      </c>
       <c r="H14" s="10" t="n">
+        <v>2487</v>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>-203</v>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>398</v>
-      </c>
       <c r="J14" s="10" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K14" s="10" t="n">
         <v>104</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="L14" s="10" t="n">
         <v>4190</v>
       </c>
-      <c r="L14" s="10" t="n">
-        <v>25165</v>
-      </c>
       <c r="M14" s="10" t="n">
+        <v>24397</v>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>-19184</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>20.93</v>
-      </c>
       <c r="O14" s="10" t="n">
-        <v>-48</v>
+        <v>28.39</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>-3.17</v>
@@ -2127,44 +2150,46 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>1135</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>700</v>
-      </c>
-      <c r="F15" s="13" t="n">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="25" t="n">
         <v>542</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>669</v>
-      </c>
       <c r="H15" s="10" t="n">
+        <v>789</v>
+      </c>
+      <c r="I15" s="10" t="n">
         <v>-43</v>
       </c>
-      <c r="I15" s="10" t="n">
-        <v>1153</v>
-      </c>
       <c r="J15" s="10" t="n">
+        <v>1041</v>
+      </c>
+      <c r="K15" s="10" t="n">
         <v>148</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="L15" s="10" t="n">
         <v>-340</v>
       </c>
-      <c r="L15" s="10" t="n">
-        <v>-728</v>
-      </c>
       <c r="M15" s="10" t="n">
-        <v>0</v>
+        <v>-819</v>
       </c>
       <c r="N15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P15" s="9" t="n">
         <v>1.66</v>
@@ -2340,44 +2365,46 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
-        <v>328</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>20787</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="24" t="n">
         <v>-1168</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>888</v>
-      </c>
       <c r="H18" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>5260</v>
-      </c>
       <c r="J18" s="10" t="n">
+        <v>5290</v>
+      </c>
+      <c r="K18" s="10" t="n">
         <v>-323</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="L18" s="10" t="n">
         <v>118</v>
       </c>
-      <c r="L18" s="10" t="n">
-        <v>-3068</v>
-      </c>
       <c r="M18" s="10" t="n">
-        <v>0</v>
+        <v>-3451</v>
       </c>
       <c r="N18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>-5.35</v>
@@ -2626,41 +2653,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>1115</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="E23" s="22" t="n">
         <v>-4.7</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="21" t="n">
         <v>4328</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="G23" s="21" t="n">
         <v>-901</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>280</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-442</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-1665</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>182</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2751</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>13202</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140184</v>
       </c>
-      <c r="N23" t="n">
-        <v>-5.27</v>
+      <c r="O23" t="n">
+        <v>-5.86</v>
       </c>
     </row>
     <row r="24">
@@ -2674,42 +2706,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="22" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="21" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="21" t="n">
         <v>-3</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>308</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>60</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-12</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-48</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>92</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2757,6 +2794,218 @@
       </c>
       <c r="N25" t="n">
         <v>7.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>980</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <v>3036</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="H26" t="n">
+        <v>563</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>108</v>
+      </c>
+      <c r="K26" t="n">
+        <v>61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>898</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4598</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-106273</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>3905</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>809</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-177</v>
+      </c>
+      <c r="K27" t="n">
+        <v>14</v>
+      </c>
+      <c r="L27" t="n">
+        <v>412</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1957</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8870</v>
+      </c>
+      <c r="O27" t="n">
+        <v>5.53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>-88</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-186</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-39</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-16</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>3807</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>-886</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-1405</v>
+      </c>
+      <c r="I29" t="n">
+        <v>57</v>
+      </c>
+      <c r="J29" t="n">
+        <v>274</v>
+      </c>
+      <c r="K29" t="n">
+        <v>113</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6520</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31932</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21566</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-4.44</v>
       </c>
     </row>
   </sheetData>
